--- a/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/tarapaca.xlsx
+++ b/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/tarapaca.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>32867.41</v>
+        <v>33093.64</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>20272.95</v>
+        <v>20607.08</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>14420.84</v>
+        <v>14480.61</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>56137.34</v>
+        <v>55526.66</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>25402.58</v>
+        <v>25537.65</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>32616.1</v>
+        <v>32716.94</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/tarapaca.xlsx
+++ b/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/tarapaca.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>794947-149-CM25</t>
+          <t>935934-149-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,27 +524,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>61.103.006-1</t>
+          <t>61.980.770-7</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Division de Bienestar Social</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
+          <t>91.502.000-3</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>33093.64</v>
+        <v>12427.09</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>6-39-CM26</t>
+          <t>794947-149-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,27 +585,27 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>61.838.000-9</t>
+          <t>61.103.006-1</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION I REGION</t>
+          <t>Division de Bienestar Social</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>79.649.140-k</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,28 +630,28 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>20607.08</v>
+        <v>33093.64</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3159-60-CM26</t>
+          <t>6-39-CM26</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -661,12 +661,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>61.102.038-4</t>
+          <t>61.838.000-9</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>DEPTO. BIENESTAR SOCIAL DE LA ARMADA (I)</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION I REGION</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>SUMMIT MOTORS S.A.</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>76.027.979-k</t>
+          <t>79.649.140-k</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>14480.61</v>
+        <v>20607.08</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3885-241-CM26</t>
+          <t>3159-60-CM26</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,12 +707,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -722,12 +722,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>69.010.400-8</t>
+          <t>61.102.038-4</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PICA</t>
+          <t>DEPTO. BIENESTAR SOCIAL DE LA ARMADA (I)</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+          <t>SUMMIT MOTORS S.A.</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>91.502.000-3</t>
+          <t>76.027.979-k</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>55526.66</v>
+        <v>14480.61</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1346281-78-CM26</t>
+          <t>3885-241-CM26</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>69.010.400-8</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>I MUNICIPALIDAD DE PICA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>79.649.140-k</t>
+          <t>91.502.000-3</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>25537.65</v>
+        <v>55526.66</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2404-799-CM26</t>
+          <t>1346281-78-CM26</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,27 +829,27 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>69.010.300-1</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE IQUIQUE</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PILMAIQUEN SPA</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>77.262.067-5</t>
+          <t>79.649.140-k</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,6 +874,67 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
+        <v>25537.65</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2404-799-CM26</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>69.010.300-1</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE IQUIQUE</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>AUTOMOTRIZ PILMAIQUEN SPA</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>77.262.067-5</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="n">
         <v>32716.94</v>
       </c>
     </row>

--- a/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/tarapaca.xlsx
+++ b/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/tarapaca.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tarapacá" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Tarapacá" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>935934-149-CM25</t>
+          <t>768-111-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,27 +524,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>jul-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>61.980.770-7</t>
+          <t>72.223.100-7</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>GOBIERNO REGIONAL DE TARAPACA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>91.502.000-3</t>
+          <t>79.649.140-k</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>12427.09</v>
+        <v>57629.98</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>794947-149-CM25</t>
+          <t>1305552-30-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,27 +585,27 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>61.103.006-1</t>
+          <t>61.981.030-9</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Division de Bienestar Social</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA TAMARUGAL</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
+          <t>86.385.500-4</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>33093.64</v>
+        <v>25747.63</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>6-39-CM26</t>
+          <t>1346281-54-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,12 +646,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -661,12 +661,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>61.838.000-9</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION I REGION</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+          <t>Comercial Motores de los Andes SpA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>79.649.140-k</t>
+          <t>76.005.909-9</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,43 +691,43 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>20607.08</v>
+        <v>29359.71</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3159-60-CM26</t>
+          <t>5908-17-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>61.102.038-4</t>
+          <t>69.010.200-5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>DEPTO. BIENESTAR SOCIAL DE LA ARMADA (I)</t>
+          <t>ILUSTRE MUNICIPALIDAD DE HUARA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,58 +737,62 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>SUMMIT MOTORS S.A.</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>76.027.979-k</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
+          <t>86.519.000-K</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>14480.61</v>
+        <v>54317.05</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3885-241-CM26</t>
+          <t>802-9-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>69.010.400-8</t>
+          <t>72.396.000-2</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PICA</t>
+          <t>CORP NACIONAL DE DESARROLLO INDIGENA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,12 +802,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>91.502.000-3</t>
+          <t>79.649.140-k</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,43 +817,43 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>55526.66</v>
+        <v>22546.55</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1346281-78-CM26</t>
+          <t>575924-81-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2025-07-24</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>60.318.000-3</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>CORP DE ASISTENCIA JUDICIAL DE LAS REG T</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -874,43 +878,43 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>25537.65</v>
+        <v>23132.37</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2404-799-CM26</t>
+          <t>935934-149-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>69.010.300-1</t>
+          <t>61.980.770-7</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE IQUIQUE</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,12 +924,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PILMAIQUEN SPA</t>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>77.262.067-5</t>
+          <t>91.502.000-3</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,7 +939,495 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
+        <v>12427.09</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>3447-2841-CM25</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>sep-2025</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>69.265.100-6</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Inchcape Camiones y Buses Chile S.A.</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>76.141.853-k</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>43643.39</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>794947-149-CM25</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>61.103.006-1</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Division de Bienestar Social</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Maritano y Ebensperger Ltda.</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>86.519.000-K</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="n">
+        <v>33093.64</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>6-39-CM26</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>61.838.000-9</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION I REGION</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>79.649.140-k</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="n">
+        <v>20607.08</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>3159-60-CM26</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>61.102.038-4</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>DEPTO. BIENESTAR SOCIAL DE LA ARMADA (I)</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>SUMMIT MOTORS S.A.</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>76.027.979-k</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="n">
+        <v>14480.61</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>3885-241-CM26</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>69.010.400-8</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PICA</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>91.502.000-3</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="n">
+        <v>55526.66</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>1346281-78-CM26</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>62.000.970-9</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>79.649.140-k</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="n">
+        <v>25537.65</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2404-799-CM26</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>69.010.300-1</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE IQUIQUE</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>AUTOMOTRIZ PILMAIQUEN SPA</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>77.262.067-5</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="n">
         <v>32716.94</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2404-1028-CM26</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>69.010.300-1</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE IQUIQUE</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Maritano y Ebensperger Ltda.</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>86.519.000-K</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="n">
+        <v>39230.06</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/tarapaca.xlsx
+++ b/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/tarapaca.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M16"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Division de Bienestar Social</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1158,7 +1158,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>DEPTO. BIENESTAR SOCIAL DE LA ARMADA (I)</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1311,7 +1311,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2404-799-CM26</t>
+          <t>2404-1028-CM26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1321,12 +1321,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PILMAIQUEN SPA</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>77.262.067-5</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1366,67 +1366,6 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>32716.94</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>2404-1028-CM26</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2239-6-LR25</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>ago-2026</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>69.010.300-1</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>I MUNICIPALIDAD DE IQUIQUE</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Tarapacá</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>Maritano y Ebensperger Ltda.</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>86.519.000-K</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="n">
         <v>39230.06</v>
       </c>
     </row>

--- a/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/tarapaca.xlsx
+++ b/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/tarapaca.xlsx
@@ -562,7 +562,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +688,11 @@
           <t>76.005.909-9</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -810,7 +818,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -871,7 +883,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -932,7 +948,11 @@
           <t>91.502.000-3</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -993,7 +1013,11 @@
           <t>76.141.853-k</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1054,7 +1078,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1115,7 +1143,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1237,7 +1269,11 @@
           <t>91.502.000-3</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1298,7 +1334,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1359,7 +1399,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/tarapaca.xlsx
+++ b/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/tarapaca.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M15"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1413,6 +1413,67 @@
         <v>39230.06</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2404-1247-CM26</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>69.010.300-1</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE IQUIQUE</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>AUTOMOTRIZ BALMACEDA LIMITADA</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>86.341.100-9</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="n">
+        <v>38090.31</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
